--- a/artfynd/A 39829-2026 artfynd.xlsx
+++ b/artfynd/A 39829-2026 artfynd.xlsx
@@ -1500,7 +1500,7 @@
         <v>137151319</v>
       </c>
       <c r="B9" t="n">
-        <v>102153</v>
+        <v>102155</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39829-2026 artfynd.xlsx
+++ b/artfynd/A 39829-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151587</v>
       </c>
       <c r="B2" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>137151319</v>
       </c>
       <c r="B9" t="n">
-        <v>102155</v>
+        <v>102157</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>137151076</v>
       </c>
       <c r="B10" t="n">
-        <v>79486</v>
+        <v>79489</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>137155828</v>
       </c>
       <c r="B11" t="n">
-        <v>79486</v>
+        <v>79489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39829-2026 artfynd.xlsx
+++ b/artfynd/A 39829-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151587</v>
       </c>
       <c r="B2" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137151157</v>
       </c>
       <c r="B3" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137153145</v>
       </c>
       <c r="B4" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137153153</v>
       </c>
       <c r="B5" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137154095</v>
       </c>
       <c r="B6" t="n">
-        <v>58647</v>
+        <v>58660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137153178</v>
       </c>
       <c r="B7" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>137153179</v>
       </c>
       <c r="B8" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>137151319</v>
       </c>
       <c r="B9" t="n">
-        <v>102157</v>
+        <v>102170</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>137151076</v>
       </c>
       <c r="B10" t="n">
-        <v>79489</v>
+        <v>79502</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>137155828</v>
       </c>
       <c r="B11" t="n">
-        <v>79489</v>
+        <v>79502</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39829-2026 artfynd.xlsx
+++ b/artfynd/A 39829-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151587</v>
       </c>
       <c r="B2" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137151157</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137153145</v>
       </c>
       <c r="B4" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137153153</v>
       </c>
       <c r="B5" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137154095</v>
       </c>
       <c r="B6" t="n">
-        <v>58660</v>
+        <v>58662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137153178</v>
       </c>
       <c r="B7" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>137153179</v>
       </c>
       <c r="B8" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>137151319</v>
       </c>
       <c r="B9" t="n">
-        <v>102170</v>
+        <v>102172</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>137151076</v>
       </c>
       <c r="B10" t="n">
-        <v>79502</v>
+        <v>79504</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>137155828</v>
       </c>
       <c r="B11" t="n">
-        <v>79502</v>
+        <v>79504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39829-2026 artfynd.xlsx
+++ b/artfynd/A 39829-2026 artfynd.xlsx
@@ -1177,11 +1177,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björnvallen, Trillevallen, Undersåker, Jmt</t>

--- a/artfynd/A 39829-2026 artfynd.xlsx
+++ b/artfynd/A 39829-2026 artfynd.xlsx
@@ -1496,7 +1496,7 @@
         <v>137151319</v>
       </c>
       <c r="B9" t="n">
-        <v>102172</v>
+        <v>102175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39829-2026 artfynd.xlsx
+++ b/artfynd/A 39829-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151587</v>
       </c>
       <c r="B2" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137151157</v>
       </c>
       <c r="B3" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137153145</v>
       </c>
       <c r="B4" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137153153</v>
       </c>
       <c r="B5" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137154095</v>
       </c>
       <c r="B6" t="n">
-        <v>58662</v>
+        <v>58672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137153178</v>
       </c>
       <c r="B7" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137153179</v>
       </c>
       <c r="B8" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137151319</v>
       </c>
       <c r="B9" t="n">
-        <v>102175</v>
+        <v>102190</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137151076</v>
       </c>
       <c r="B10" t="n">
-        <v>79504</v>
+        <v>79514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>137155828</v>
       </c>
       <c r="B11" t="n">
-        <v>79504</v>
+        <v>79514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39829-2026 artfynd.xlsx
+++ b/artfynd/A 39829-2026 artfynd.xlsx
@@ -1496,7 +1496,7 @@
         <v>137151319</v>
       </c>
       <c r="B9" t="n">
-        <v>102190</v>
+        <v>102191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39829-2026 artfynd.xlsx
+++ b/artfynd/A 39829-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151587</v>
       </c>
       <c r="B2" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137151157</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137153145</v>
       </c>
       <c r="B4" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137153153</v>
       </c>
       <c r="B5" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137154095</v>
       </c>
       <c r="B6" t="n">
-        <v>58672</v>
+        <v>58674</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137153178</v>
       </c>
       <c r="B7" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137153179</v>
       </c>
       <c r="B8" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137151319</v>
       </c>
       <c r="B9" t="n">
-        <v>102191</v>
+        <v>102196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137151076</v>
       </c>
       <c r="B10" t="n">
-        <v>79514</v>
+        <v>79517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>137155828</v>
       </c>
       <c r="B11" t="n">
-        <v>79514</v>
+        <v>79517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39829-2026 artfynd.xlsx
+++ b/artfynd/A 39829-2026 artfynd.xlsx
@@ -1496,7 +1496,7 @@
         <v>137151319</v>
       </c>
       <c r="B9" t="n">
-        <v>102196</v>
+        <v>102199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39829-2026 artfynd.xlsx
+++ b/artfynd/A 39829-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151587</v>
       </c>
       <c r="B2" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137151157</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137153145</v>
       </c>
       <c r="B4" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137153153</v>
       </c>
       <c r="B5" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137154095</v>
       </c>
       <c r="B6" t="n">
-        <v>58674</v>
+        <v>58676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137153178</v>
       </c>
       <c r="B7" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137153179</v>
       </c>
       <c r="B8" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137151319</v>
       </c>
       <c r="B9" t="n">
-        <v>102199</v>
+        <v>102205</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137151076</v>
       </c>
       <c r="B10" t="n">
-        <v>79517</v>
+        <v>79522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>137155828</v>
       </c>
       <c r="B11" t="n">
-        <v>79517</v>
+        <v>79522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39829-2026 artfynd.xlsx
+++ b/artfynd/A 39829-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151587</v>
       </c>
       <c r="B2" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137151319</v>
       </c>
       <c r="B9" t="n">
-        <v>102205</v>
+        <v>102217</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137151076</v>
       </c>
       <c r="B10" t="n">
-        <v>79522</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>137155828</v>
       </c>
       <c r="B11" t="n">
-        <v>79522</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39829-2026 artfynd.xlsx
+++ b/artfynd/A 39829-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151587</v>
       </c>
       <c r="B2" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137151319</v>
       </c>
       <c r="B9" t="n">
-        <v>102217</v>
+        <v>102218</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137151076</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79534</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>137155828</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79534</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39829-2026 artfynd.xlsx
+++ b/artfynd/A 39829-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151587</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137151319</v>
       </c>
       <c r="B9" t="n">
-        <v>102218</v>
+        <v>102221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137151076</v>
       </c>
       <c r="B10" t="n">
-        <v>79534</v>
+        <v>79536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>137155828</v>
       </c>
       <c r="B11" t="n">
-        <v>79534</v>
+        <v>79536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39829-2026 artfynd.xlsx
+++ b/artfynd/A 39829-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151587</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137151157</v>
       </c>
       <c r="B3" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137153145</v>
       </c>
       <c r="B4" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137153153</v>
       </c>
       <c r="B5" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137154095</v>
       </c>
       <c r="B6" t="n">
-        <v>58676</v>
+        <v>58679</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137153178</v>
       </c>
       <c r="B7" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137153179</v>
       </c>
       <c r="B8" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137151319</v>
       </c>
       <c r="B9" t="n">
-        <v>102221</v>
+        <v>102225</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137151076</v>
       </c>
       <c r="B10" t="n">
-        <v>79536</v>
+        <v>79540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>137155828</v>
       </c>
       <c r="B11" t="n">
-        <v>79536</v>
+        <v>79540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
